--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17047" uniqueCount="8528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17089" uniqueCount="8549">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,69 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>LS-2025-000165-MYS</t>
+  </si>
+  <si>
+    <t>EQ-2025-000164-IND</t>
+  </si>
+  <si>
+    <t>WF-2025-000163-BOL</t>
+  </si>
+  <si>
+    <t>EQ-2025-000162-RUS</t>
+  </si>
+  <si>
+    <t>FL-2025-000161-IDN</t>
+  </si>
+  <si>
+    <t>TC-2025-000160-CHN</t>
+  </si>
+  <si>
+    <t>EQ-2025-000159-AFG</t>
+  </si>
+  <si>
+    <t>FL-2025-000158-SSD</t>
+  </si>
+  <si>
+    <t>EP-2025-000157-COD</t>
+  </si>
+  <si>
+    <t>EQ-2025-000156-AFG</t>
+  </si>
+  <si>
+    <t>FR-2025-000155-KAZ</t>
+  </si>
+  <si>
+    <t>FL-2025-000154-SDN</t>
+  </si>
+  <si>
+    <t>EQ-2025-000153-AFG</t>
+  </si>
+  <si>
+    <t>DR-2025-000152-SYR</t>
+  </si>
+  <si>
+    <t>FL-2025-000151-YEM</t>
+  </si>
+  <si>
+    <t>FL-2025-000150-GIN</t>
+  </si>
+  <si>
+    <t>EP-2025-000149-TCD</t>
+  </si>
+  <si>
+    <t>DR-2025-000148-ETH</t>
+  </si>
+  <si>
+    <t>FL-2025-000147-CPV</t>
+  </si>
+  <si>
+    <t>FL-2025-000146-CPV</t>
+  </si>
+  <si>
+    <t>FL-2025-000145-GNQ</t>
   </si>
   <si>
     <t>TC-2025-000144-VNM</t>
@@ -25929,7 +25992,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8521"/>
+  <dimension ref="A1:G8542"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94115,6 +94178,174 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8522" spans="1:4">
+      <c r="A8522" t="s">
+        <v>8528</v>
+      </c>
+      <c r="D8522" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8523" spans="1:4">
+      <c r="A8523" t="s">
+        <v>8529</v>
+      </c>
+      <c r="D8523" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8524" spans="1:4">
+      <c r="A8524" t="s">
+        <v>8530</v>
+      </c>
+      <c r="D8524" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8525" spans="1:4">
+      <c r="A8525" t="s">
+        <v>8531</v>
+      </c>
+      <c r="D8525" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8526" spans="1:4">
+      <c r="A8526" t="s">
+        <v>8532</v>
+      </c>
+      <c r="D8526" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8527" spans="1:4">
+      <c r="A8527" t="s">
+        <v>8533</v>
+      </c>
+      <c r="D8527" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8528" spans="1:4">
+      <c r="A8528" t="s">
+        <v>8534</v>
+      </c>
+      <c r="D8528" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8529" spans="1:4">
+      <c r="A8529" t="s">
+        <v>8535</v>
+      </c>
+      <c r="D8529" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8530" spans="1:4">
+      <c r="A8530" t="s">
+        <v>8536</v>
+      </c>
+      <c r="D8530" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8531" spans="1:4">
+      <c r="A8531" t="s">
+        <v>8537</v>
+      </c>
+      <c r="D8531" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8532" spans="1:4">
+      <c r="A8532" t="s">
+        <v>8538</v>
+      </c>
+      <c r="D8532" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8533" spans="1:4">
+      <c r="A8533" t="s">
+        <v>8539</v>
+      </c>
+      <c r="D8533" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8534" spans="1:4">
+      <c r="A8534" t="s">
+        <v>8540</v>
+      </c>
+      <c r="D8534" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8535" spans="1:4">
+      <c r="A8535" t="s">
+        <v>8541</v>
+      </c>
+      <c r="D8535" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8536" spans="1:4">
+      <c r="A8536" t="s">
+        <v>8542</v>
+      </c>
+      <c r="D8536" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8537" spans="1:4">
+      <c r="A8537" t="s">
+        <v>8543</v>
+      </c>
+      <c r="D8537" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8538" spans="1:4">
+      <c r="A8538" t="s">
+        <v>8544</v>
+      </c>
+      <c r="D8538" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8539" spans="1:4">
+      <c r="A8539" t="s">
+        <v>8545</v>
+      </c>
+      <c r="D8539" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8540" spans="1:4">
+      <c r="A8540" t="s">
+        <v>8546</v>
+      </c>
+      <c r="D8540" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8541" spans="1:4">
+      <c r="A8541" t="s">
+        <v>8547</v>
+      </c>
+      <c r="D8541" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8542" spans="1:4">
+      <c r="A8542" t="s">
+        <v>8548</v>
+      </c>
+      <c r="D8542" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17089" uniqueCount="8549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17107" uniqueCount="8558">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,30 @@
     <t>en</t>
   </si>
   <si>
+    <t>TC-2025-000170-CHN</t>
+  </si>
+  <si>
+    <t>TC-2025-000170-PHL</t>
+  </si>
+  <si>
+    <t>TC-2025-000170-TWN</t>
+  </si>
+  <si>
+    <t>TC-2025-000170-VNM</t>
+  </si>
+  <si>
+    <t>FL-2025-000169-SLE</t>
+  </si>
+  <si>
+    <t>FL-2025-000168-SSD</t>
+  </si>
+  <si>
+    <t>TC-2025-000167-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2025-000166-RUS</t>
+  </si>
+  <si>
     <t>LS-2025-000165-MYS</t>
   </si>
   <si>
@@ -554,6 +578,9 @@
   </si>
   <si>
     <t>EQ-2025-000001-ETH</t>
+  </si>
+  <si>
+    <t>FL-2024-000235-BEN</t>
   </si>
   <si>
     <t>DR-2024-000234-PNG</t>
@@ -25992,7 +26019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8542"/>
+  <dimension ref="A1:G8551"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94346,6 +94373,78 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8543" spans="1:4">
+      <c r="A8543" t="s">
+        <v>8549</v>
+      </c>
+      <c r="D8543" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8544" spans="1:4">
+      <c r="A8544" t="s">
+        <v>8550</v>
+      </c>
+      <c r="D8544" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8545" spans="1:4">
+      <c r="A8545" t="s">
+        <v>8551</v>
+      </c>
+      <c r="D8545" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8546" spans="1:4">
+      <c r="A8546" t="s">
+        <v>8552</v>
+      </c>
+      <c r="D8546" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8547" spans="1:4">
+      <c r="A8547" t="s">
+        <v>8553</v>
+      </c>
+      <c r="D8547" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8548" spans="1:4">
+      <c r="A8548" t="s">
+        <v>8554</v>
+      </c>
+      <c r="D8548" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8549" spans="1:4">
+      <c r="A8549" t="s">
+        <v>8555</v>
+      </c>
+      <c r="D8549" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8550" spans="1:4">
+      <c r="A8550" t="s">
+        <v>8556</v>
+      </c>
+      <c r="D8550" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8551" spans="1:4">
+      <c r="A8551" t="s">
+        <v>8557</v>
+      </c>
+      <c r="D8551" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17107" uniqueCount="8558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17121" uniqueCount="8565">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,27 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2025-000177-YEM</t>
+  </si>
+  <si>
+    <t>TC-2025-000176-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2025-000175-VEN</t>
+  </si>
+  <si>
+    <t>FL-2025-000174-HTI</t>
+  </si>
+  <si>
+    <t>EQ-2025-000173-VEN</t>
+  </si>
+  <si>
+    <t>DR-2025-000172-SOM</t>
+  </si>
+  <si>
+    <t>FL-2025-000171-IND</t>
   </si>
   <si>
     <t>TC-2025-000170-CHN</t>
@@ -26019,7 +26040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8551"/>
+  <dimension ref="A1:G8558"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94445,6 +94466,62 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8552" spans="1:4">
+      <c r="A8552" t="s">
+        <v>8558</v>
+      </c>
+      <c r="D8552" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8553" spans="1:4">
+      <c r="A8553" t="s">
+        <v>8559</v>
+      </c>
+      <c r="D8553" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8554" spans="1:4">
+      <c r="A8554" t="s">
+        <v>8560</v>
+      </c>
+      <c r="D8554" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8555" spans="1:4">
+      <c r="A8555" t="s">
+        <v>8561</v>
+      </c>
+      <c r="D8555" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8556" spans="1:4">
+      <c r="A8556" t="s">
+        <v>8562</v>
+      </c>
+      <c r="D8556" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8557" spans="1:4">
+      <c r="A8557" t="s">
+        <v>8563</v>
+      </c>
+      <c r="D8557" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8558" spans="1:4">
+      <c r="A8558" t="s">
+        <v>8564</v>
+      </c>
+      <c r="D8558" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17121" uniqueCount="8565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17143" uniqueCount="8576">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,39 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>EQ-2025-000188-CHN</t>
+  </si>
+  <si>
+    <t>FL-2025-000187-NGA</t>
+  </si>
+  <si>
+    <t>TC-2025-000186-VNM</t>
+  </si>
+  <si>
+    <t>FF-2025-000185-GEO</t>
+  </si>
+  <si>
+    <t>FL-2025-000184-NPL</t>
+  </si>
+  <si>
+    <t>TC-2025-000183-VNM</t>
+  </si>
+  <si>
+    <t>EP-2025-000182-SOM</t>
+  </si>
+  <si>
+    <t>EQ-2025-000181-PHL</t>
+  </si>
+  <si>
+    <t>DR-2025-000180-CHN</t>
+  </si>
+  <si>
+    <t>TC-2025-000179-VNM</t>
+  </si>
+  <si>
+    <t>FL-2025-000178-CHN</t>
   </si>
   <si>
     <t>FL-2025-000177-YEM</t>
@@ -26040,7 +26073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8558"/>
+  <dimension ref="A1:G8569"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94522,6 +94555,94 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8559" spans="1:4">
+      <c r="A8559" t="s">
+        <v>8565</v>
+      </c>
+      <c r="D8559" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8560" spans="1:4">
+      <c r="A8560" t="s">
+        <v>8566</v>
+      </c>
+      <c r="D8560" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8561" spans="1:4">
+      <c r="A8561" t="s">
+        <v>8567</v>
+      </c>
+      <c r="D8561" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8562" spans="1:4">
+      <c r="A8562" t="s">
+        <v>8568</v>
+      </c>
+      <c r="D8562" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8563" spans="1:4">
+      <c r="A8563" t="s">
+        <v>8569</v>
+      </c>
+      <c r="D8563" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8564" spans="1:4">
+      <c r="A8564" t="s">
+        <v>8570</v>
+      </c>
+      <c r="D8564" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8565" spans="1:4">
+      <c r="A8565" t="s">
+        <v>8571</v>
+      </c>
+      <c r="D8565" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8566" spans="1:4">
+      <c r="A8566" t="s">
+        <v>8572</v>
+      </c>
+      <c r="D8566" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8567" spans="1:4">
+      <c r="A8567" t="s">
+        <v>8573</v>
+      </c>
+      <c r="D8567" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8568" spans="1:4">
+      <c r="A8568" t="s">
+        <v>8574</v>
+      </c>
+      <c r="D8568" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8569" spans="1:4">
+      <c r="A8569" t="s">
+        <v>8575</v>
+      </c>
+      <c r="D8569" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17143" uniqueCount="8576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17153" uniqueCount="8581">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,21 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2025-000193-MEX</t>
+  </si>
+  <si>
+    <t>EQ-2025-000192-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2025-000191-ETH</t>
+  </si>
+  <si>
+    <t>FL-2025-000190-EGY</t>
+  </si>
+  <si>
+    <t>EQ-2025-000189-PHL</t>
   </si>
   <si>
     <t>EQ-2025-000188-CHN</t>
@@ -26073,7 +26088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8569"/>
+  <dimension ref="A1:G8574"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94643,6 +94658,46 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8570" spans="1:4">
+      <c r="A8570" t="s">
+        <v>8576</v>
+      </c>
+      <c r="D8570" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8571" spans="1:4">
+      <c r="A8571" t="s">
+        <v>8577</v>
+      </c>
+      <c r="D8571" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8572" spans="1:4">
+      <c r="A8572" t="s">
+        <v>8578</v>
+      </c>
+      <c r="D8572" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8573" spans="1:4">
+      <c r="A8573" t="s">
+        <v>8579</v>
+      </c>
+      <c r="D8573" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8574" spans="1:4">
+      <c r="A8574" t="s">
+        <v>8580</v>
+      </c>
+      <c r="D8574" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17153" uniqueCount="8581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17161" uniqueCount="8585">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,18 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2025-000196-HTI</t>
+  </si>
+  <si>
+    <t>TC-2025-000195-PHL</t>
+  </si>
+  <si>
+    <t>TC-2025-000195-VNM</t>
+  </si>
+  <si>
+    <t>VO-2025-000194-IDN</t>
   </si>
   <si>
     <t>FL-2025-000193-MEX</t>
@@ -26088,7 +26100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8574"/>
+  <dimension ref="A1:G8578"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94698,6 +94710,38 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8575" spans="1:4">
+      <c r="A8575" t="s">
+        <v>8581</v>
+      </c>
+      <c r="D8575" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8576" spans="1:4">
+      <c r="A8576" t="s">
+        <v>8582</v>
+      </c>
+      <c r="D8576" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8577" spans="1:4">
+      <c r="A8577" t="s">
+        <v>8583</v>
+      </c>
+      <c r="D8577" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8578" spans="1:4">
+      <c r="A8578" t="s">
+        <v>8584</v>
+      </c>
+      <c r="D8578" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17161" uniqueCount="8585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17175" uniqueCount="8592">
   <si>
     <t>code</t>
   </si>
@@ -43,7 +43,28 @@
     <t>en</t>
   </si>
   <si>
+    <t>EQ-2025-000202-AFG</t>
+  </si>
+  <si>
+    <t>FL-2025-000201-CUB</t>
+  </si>
+  <si>
+    <t>EP-2025-000200-CUB</t>
+  </si>
+  <si>
+    <t>AV-2025-000199-TJK</t>
+  </si>
+  <si>
+    <t>FL-2025-000198-VNM</t>
+  </si>
+  <si>
+    <t>EQ-2025-000197-TUR</t>
+  </si>
+  <si>
     <t>TC-2025-000196-HTI</t>
+  </si>
+  <si>
+    <t>TC-2025-000196-JAM</t>
   </si>
   <si>
     <t>TC-2025-000195-PHL</t>
@@ -26100,7 +26121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8578"/>
+  <dimension ref="A1:G8585"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94742,6 +94763,62 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8579" spans="1:4">
+      <c r="A8579" t="s">
+        <v>8585</v>
+      </c>
+      <c r="D8579" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8580" spans="1:4">
+      <c r="A8580" t="s">
+        <v>8586</v>
+      </c>
+      <c r="D8580" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8581" spans="1:4">
+      <c r="A8581" t="s">
+        <v>8587</v>
+      </c>
+      <c r="D8581" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8582" spans="1:4">
+      <c r="A8582" t="s">
+        <v>8588</v>
+      </c>
+      <c r="D8582" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8583" spans="1:4">
+      <c r="A8583" t="s">
+        <v>8589</v>
+      </c>
+      <c r="D8583" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8584" spans="1:4">
+      <c r="A8584" t="s">
+        <v>8590</v>
+      </c>
+      <c r="D8584" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8585" spans="1:4">
+      <c r="A8585" t="s">
+        <v>8591</v>
+      </c>
+      <c r="D8585" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17175" uniqueCount="8592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17177" uniqueCount="8593">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2025-000203-PHL</t>
   </si>
   <si>
     <t>EQ-2025-000202-AFG</t>
@@ -26121,7 +26124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8585"/>
+  <dimension ref="A1:G8586"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94819,6 +94822,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8586" spans="1:4">
+      <c r="A8586" t="s">
+        <v>8592</v>
+      </c>
+      <c r="D8586" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17177" uniqueCount="8593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17289" uniqueCount="8649">
   <si>
     <t>code</t>
   </si>
@@ -43,9 +43,111 @@
     <t>en</t>
   </si>
   <si>
+    <t>FL-2026-000006-TUN</t>
+  </si>
+  <si>
+    <t>FL-2026-000005-MKD</t>
+  </si>
+  <si>
+    <t>FL-2026-000004-MOZ</t>
+  </si>
+  <si>
+    <t>WF-2026-000003-CHL</t>
+  </si>
+  <si>
+    <t>CW-2026-000002-SRB</t>
+  </si>
+  <si>
+    <t>FL-2026-000001-MYS</t>
+  </si>
+  <si>
+    <t>EP-2025-000230-MDG</t>
+  </si>
+  <si>
+    <t>FL-2025-000229-CMR</t>
+  </si>
+  <si>
+    <t>FL-2025-000228-MOZ</t>
+  </si>
+  <si>
+    <t>FL-2025-000227-MOZ</t>
+  </si>
+  <si>
+    <t>CW-2025-000226-SYR</t>
+  </si>
+  <si>
+    <t>FF-2025-000225-IRN</t>
+  </si>
+  <si>
+    <t>FL-2025-000224-PSE</t>
+  </si>
+  <si>
+    <t>FF-2025-000223-MAR</t>
+  </si>
+  <si>
+    <t>FF-2025-000222-IRQ</t>
+  </si>
+  <si>
+    <t>WF-2025-000221-IRN</t>
+  </si>
+  <si>
+    <t>EQ-2025-000220-JPN</t>
+  </si>
+  <si>
+    <t>FL-2025-000219-COG</t>
+  </si>
+  <si>
+    <t>TC-2025-000218-LKA</t>
+  </si>
+  <si>
+    <t>FL-2025-000217-IDN</t>
+  </si>
+  <si>
+    <t>FL-2025-000216-LKA</t>
+  </si>
+  <si>
+    <t>EP-2025-000215-ETH</t>
+  </si>
+  <si>
+    <t>FL-2025-000213-LKA</t>
+  </si>
+  <si>
+    <t>LS-2025-000212-IDN</t>
+  </si>
+  <si>
+    <t>FL-2025-000211-MYS</t>
+  </si>
+  <si>
+    <t>FL-2025-000210-THA</t>
+  </si>
+  <si>
+    <t>FL-2025-000209-THA</t>
+  </si>
+  <si>
+    <t>EQ-2025-000208-BGD</t>
+  </si>
+  <si>
+    <t>FL-2025-000207-VNM</t>
+  </si>
+  <si>
+    <t>VO-2025-000206-IDN</t>
+  </si>
+  <si>
+    <t>LS-2025-000205-IDN</t>
+  </si>
+  <si>
+    <t>TC-2025-000204-PHL</t>
+  </si>
+  <si>
+    <t>TC-2025-000204-TWN</t>
+  </si>
+  <si>
     <t>TC-2025-000203-PHL</t>
   </si>
   <si>
+    <t>TC-2025-000203-VNM</t>
+  </si>
+  <si>
     <t>EQ-2025-000202-AFG</t>
   </si>
   <si>
@@ -683,6 +785,72 @@
   </si>
   <si>
     <t>EQ-2025-000001-ETH</t>
+  </si>
+  <si>
+    <t>TO-2024-000257-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000256-USA</t>
+  </si>
+  <si>
+    <t>DR-2024-000255-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000254-USA</t>
+  </si>
+  <si>
+    <t>CW-2024-000253-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000252-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000251-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000250-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000249-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000248-USA</t>
+  </si>
+  <si>
+    <t>TC-2024-000247-USA</t>
+  </si>
+  <si>
+    <t>TC-2024-000246-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000245-USA</t>
+  </si>
+  <si>
+    <t>TC-2024-000244-USA</t>
+  </si>
+  <si>
+    <t>WF-2024-000243-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000242-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000241-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000240-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000239-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000238-USA</t>
+  </si>
+  <si>
+    <t>ST-2024-000237-USA</t>
+  </si>
+  <si>
+    <t>TO-2024-000236-USA</t>
   </si>
   <si>
     <t>FL-2024-000235-BEN</t>
@@ -26124,7 +26292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8586"/>
+  <dimension ref="A1:G8642"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -94830,6 +94998,454 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8587" spans="1:4">
+      <c r="A8587" t="s">
+        <v>8593</v>
+      </c>
+      <c r="D8587" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8588" spans="1:4">
+      <c r="A8588" t="s">
+        <v>8594</v>
+      </c>
+      <c r="D8588" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8589" spans="1:4">
+      <c r="A8589" t="s">
+        <v>8595</v>
+      </c>
+      <c r="D8589" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8590" spans="1:4">
+      <c r="A8590" t="s">
+        <v>8596</v>
+      </c>
+      <c r="D8590" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8591" spans="1:4">
+      <c r="A8591" t="s">
+        <v>8597</v>
+      </c>
+      <c r="D8591" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8592" spans="1:4">
+      <c r="A8592" t="s">
+        <v>8598</v>
+      </c>
+      <c r="D8592" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8593" spans="1:4">
+      <c r="A8593" t="s">
+        <v>8599</v>
+      </c>
+      <c r="D8593" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8594" spans="1:4">
+      <c r="A8594" t="s">
+        <v>8600</v>
+      </c>
+      <c r="D8594" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8595" spans="1:4">
+      <c r="A8595" t="s">
+        <v>8601</v>
+      </c>
+      <c r="D8595" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8596" spans="1:4">
+      <c r="A8596" t="s">
+        <v>8602</v>
+      </c>
+      <c r="D8596" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8597" spans="1:4">
+      <c r="A8597" t="s">
+        <v>8603</v>
+      </c>
+      <c r="D8597" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8598" spans="1:4">
+      <c r="A8598" t="s">
+        <v>8604</v>
+      </c>
+      <c r="D8598" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8599" spans="1:4">
+      <c r="A8599" t="s">
+        <v>8605</v>
+      </c>
+      <c r="D8599" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8600" spans="1:4">
+      <c r="A8600" t="s">
+        <v>8606</v>
+      </c>
+      <c r="D8600" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8601" spans="1:4">
+      <c r="A8601" t="s">
+        <v>8607</v>
+      </c>
+      <c r="D8601" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8602" spans="1:4">
+      <c r="A8602" t="s">
+        <v>8608</v>
+      </c>
+      <c r="D8602" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8603" spans="1:4">
+      <c r="A8603" t="s">
+        <v>8609</v>
+      </c>
+      <c r="D8603" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8604" spans="1:4">
+      <c r="A8604" t="s">
+        <v>8610</v>
+      </c>
+      <c r="D8604" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8605" spans="1:4">
+      <c r="A8605" t="s">
+        <v>8611</v>
+      </c>
+      <c r="D8605" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8606" spans="1:4">
+      <c r="A8606" t="s">
+        <v>8612</v>
+      </c>
+      <c r="D8606" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8607" spans="1:4">
+      <c r="A8607" t="s">
+        <v>8613</v>
+      </c>
+      <c r="D8607" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8608" spans="1:4">
+      <c r="A8608" t="s">
+        <v>8614</v>
+      </c>
+      <c r="D8608" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8609" spans="1:4">
+      <c r="A8609" t="s">
+        <v>8615</v>
+      </c>
+      <c r="D8609" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8610" spans="1:4">
+      <c r="A8610" t="s">
+        <v>8616</v>
+      </c>
+      <c r="D8610" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8611" spans="1:4">
+      <c r="A8611" t="s">
+        <v>8617</v>
+      </c>
+      <c r="D8611" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8612" spans="1:4">
+      <c r="A8612" t="s">
+        <v>8618</v>
+      </c>
+      <c r="D8612" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8613" spans="1:4">
+      <c r="A8613" t="s">
+        <v>8619</v>
+      </c>
+      <c r="D8613" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8614" spans="1:4">
+      <c r="A8614" t="s">
+        <v>8620</v>
+      </c>
+      <c r="D8614" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8615" spans="1:4">
+      <c r="A8615" t="s">
+        <v>8621</v>
+      </c>
+      <c r="D8615" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8616" spans="1:4">
+      <c r="A8616" t="s">
+        <v>8622</v>
+      </c>
+      <c r="D8616" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8617" spans="1:4">
+      <c r="A8617" t="s">
+        <v>8623</v>
+      </c>
+      <c r="D8617" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8618" spans="1:4">
+      <c r="A8618" t="s">
+        <v>8624</v>
+      </c>
+      <c r="D8618" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8619" spans="1:4">
+      <c r="A8619" t="s">
+        <v>8625</v>
+      </c>
+      <c r="D8619" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8620" spans="1:4">
+      <c r="A8620" t="s">
+        <v>8626</v>
+      </c>
+      <c r="D8620" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8621" spans="1:4">
+      <c r="A8621" t="s">
+        <v>8627</v>
+      </c>
+      <c r="D8621" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8622" spans="1:4">
+      <c r="A8622" t="s">
+        <v>8628</v>
+      </c>
+      <c r="D8622" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8623" spans="1:4">
+      <c r="A8623" t="s">
+        <v>8629</v>
+      </c>
+      <c r="D8623" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8624" spans="1:4">
+      <c r="A8624" t="s">
+        <v>8630</v>
+      </c>
+      <c r="D8624" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8625" spans="1:4">
+      <c r="A8625" t="s">
+        <v>8631</v>
+      </c>
+      <c r="D8625" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8626" spans="1:4">
+      <c r="A8626" t="s">
+        <v>8632</v>
+      </c>
+      <c r="D8626" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8627" spans="1:4">
+      <c r="A8627" t="s">
+        <v>8633</v>
+      </c>
+      <c r="D8627" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8628" spans="1:4">
+      <c r="A8628" t="s">
+        <v>8634</v>
+      </c>
+      <c r="D8628" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8629" spans="1:4">
+      <c r="A8629" t="s">
+        <v>8635</v>
+      </c>
+      <c r="D8629" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8630" spans="1:4">
+      <c r="A8630" t="s">
+        <v>8636</v>
+      </c>
+      <c r="D8630" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8631" spans="1:4">
+      <c r="A8631" t="s">
+        <v>8637</v>
+      </c>
+      <c r="D8631" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8632" spans="1:4">
+      <c r="A8632" t="s">
+        <v>8638</v>
+      </c>
+      <c r="D8632" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8633" spans="1:4">
+      <c r="A8633" t="s">
+        <v>8639</v>
+      </c>
+      <c r="D8633" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8634" spans="1:4">
+      <c r="A8634" t="s">
+        <v>8640</v>
+      </c>
+      <c r="D8634" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8635" spans="1:4">
+      <c r="A8635" t="s">
+        <v>8641</v>
+      </c>
+      <c r="D8635" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8636" spans="1:4">
+      <c r="A8636" t="s">
+        <v>8642</v>
+      </c>
+      <c r="D8636" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8637" spans="1:4">
+      <c r="A8637" t="s">
+        <v>8643</v>
+      </c>
+      <c r="D8637" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8638" spans="1:4">
+      <c r="A8638" t="s">
+        <v>8644</v>
+      </c>
+      <c r="D8638" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8639" spans="1:4">
+      <c r="A8639" t="s">
+        <v>8645</v>
+      </c>
+      <c r="D8639" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8640" spans="1:4">
+      <c r="A8640" t="s">
+        <v>8646</v>
+      </c>
+      <c r="D8640" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8641" spans="1:4">
+      <c r="A8641" t="s">
+        <v>8647</v>
+      </c>
+      <c r="D8641" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8642" spans="1:4">
+      <c r="A8642" t="s">
+        <v>8648</v>
+      </c>
+      <c r="D8642" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17289" uniqueCount="8649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17561" uniqueCount="8785">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,360 @@
     <t>en</t>
   </si>
   <si>
+    <t>FL-2026-000114-KGZ</t>
+  </si>
+  <si>
+    <t>WF-2026-000113-ESP</t>
+  </si>
+  <si>
+    <t>WF-2026-000112-FRA</t>
+  </si>
+  <si>
+    <t>FL-2026-000111-TJK</t>
+  </si>
+  <si>
+    <t>FL-2026-000110-BGD</t>
+  </si>
+  <si>
+    <t>FL-2026-000109-BGD</t>
+  </si>
+  <si>
+    <t>LS-2026-000108-CHN</t>
+  </si>
+  <si>
+    <t>EP-2026-000107-CAF</t>
+  </si>
+  <si>
+    <t>FL-2026-000106-GEO</t>
+  </si>
+  <si>
+    <t>FL-2026-000105-CHN</t>
+  </si>
+  <si>
+    <t>LS-2026-000104-KGZ</t>
+  </si>
+  <si>
+    <t>OT-2026-000103-KGZ</t>
+  </si>
+  <si>
+    <t>WF-2026-000102-FRA</t>
+  </si>
+  <si>
+    <t>WF-2026-000101-PRT</t>
+  </si>
+  <si>
+    <t>FL-2026-000100-KAZ</t>
+  </si>
+  <si>
+    <t>LS-2026-000099-PHL</t>
+  </si>
+  <si>
+    <t>TC-2026-000099-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000099-GUM</t>
+  </si>
+  <si>
+    <t>TC-2026-000099-TWN</t>
+  </si>
+  <si>
+    <t>TC-2026-000098-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000098-VNM</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-CHE</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-DEU</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-ESP</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-FRA</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-GBR</t>
+  </si>
+  <si>
+    <t>HT-2026-000097-NLD</t>
+  </si>
+  <si>
+    <t>EQ-2026-000096-JPN</t>
+  </si>
+  <si>
+    <t>EP-2026-000095-IRQ</t>
+  </si>
+  <si>
+    <t>EQ-2026-000094-JPN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000093-VEN</t>
+  </si>
+  <si>
+    <t>LS-2026-000092-JPN</t>
+  </si>
+  <si>
+    <t>FL-2026-000091-MDA</t>
+  </si>
+  <si>
+    <t>TC-2026-000090-JPN</t>
+  </si>
+  <si>
+    <t>TC-2026-000090-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2026-000089-IDN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000088-CHN</t>
+  </si>
+  <si>
+    <t>FL-2026-000087-DOM</t>
+  </si>
+  <si>
+    <t>ST-2026-000086-ARM</t>
+  </si>
+  <si>
+    <t>EP-2026-000085-LKA</t>
+  </si>
+  <si>
+    <t>EQ-2026-000084-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2026-000083-IDN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000083-PHL</t>
+  </si>
+  <si>
+    <t>OT-2026-000082-KGZ</t>
+  </si>
+  <si>
+    <t>LS-2026-000081-KGZ</t>
+  </si>
+  <si>
+    <t>FL-2026-000080-SYR</t>
+  </si>
+  <si>
+    <t>EP-2026-000079-SLE</t>
+  </si>
+  <si>
+    <t>TC-2026-000078-JPN</t>
+  </si>
+  <si>
+    <t>TC-2026-000078-PHL</t>
+  </si>
+  <si>
+    <t>FL-2026-000077-UZB</t>
+  </si>
+  <si>
+    <t>FL-2026-000076-KGZ</t>
+  </si>
+  <si>
+    <t>FL-2026-000075-CHN</t>
+  </si>
+  <si>
+    <t>FF-2026-000074-AFG</t>
+  </si>
+  <si>
+    <t>EQ-2026-000073-CHN</t>
+  </si>
+  <si>
+    <t>ST-2026-000072-IND</t>
+  </si>
+  <si>
+    <t>EP-2026-000071-COD</t>
+  </si>
+  <si>
+    <t>FL-2026-000069-KEN</t>
+  </si>
+  <si>
+    <t>VO-2026-000068-IDN</t>
+  </si>
+  <si>
+    <t>FL-2026-000067-TJK</t>
+  </si>
+  <si>
+    <t>FL-2026-000066-KGZ</t>
+  </si>
+  <si>
+    <t>VO-2026-000065-PHL</t>
+  </si>
+  <si>
+    <t>FR-2026-000064-MYS</t>
+  </si>
+  <si>
+    <t>FL-2026-000063-TZA</t>
+  </si>
+  <si>
+    <t>ST-2026-000062-VNM</t>
+  </si>
+  <si>
+    <t>ST-2026-000061-THA</t>
+  </si>
+  <si>
+    <t>WF-2026-000060-JPN</t>
+  </si>
+  <si>
+    <t>FL-2026-000059-NZL</t>
+  </si>
+  <si>
+    <t>FL-2026-000058-HTI</t>
+  </si>
+  <si>
+    <t>EQ-2026-000057-JPN</t>
+  </si>
+  <si>
+    <t>FL-2026-000056-CAN</t>
+  </si>
+  <si>
+    <t>FR-2026-000055-GNB</t>
+  </si>
+  <si>
+    <t>VW-2026-000054-LBR</t>
+  </si>
+  <si>
+    <t>TC-2026-000053-FJI</t>
+  </si>
+  <si>
+    <t>FR-2026-000052-LBR</t>
+  </si>
+  <si>
+    <t>TC-2026-000051-PNG</t>
+  </si>
+  <si>
+    <t>TC-2026-000051-SLB</t>
+  </si>
+  <si>
+    <t>TC-2026-000050-FSM</t>
+  </si>
+  <si>
+    <t>EP-2026-000048-BGD</t>
+  </si>
+  <si>
+    <t>FL-2026-000047-AFG</t>
+  </si>
+  <si>
+    <t>FL-2026-000046-BWA</t>
+  </si>
+  <si>
+    <t>FL-2026-000045-KAZ</t>
+  </si>
+  <si>
+    <t>FL-2026-000044-YEM</t>
+  </si>
+  <si>
+    <t>FF-2026-000043-AFG</t>
+  </si>
+  <si>
+    <t>EQ-2026-000042-VUT</t>
+  </si>
+  <si>
+    <t>LS-2026-000041-ARG</t>
+  </si>
+  <si>
+    <t>FL-2026-000040-RWA</t>
+  </si>
+  <si>
+    <t>EP-2026-000039-SOM</t>
+  </si>
+  <si>
+    <t>FL-2026-000038-PER</t>
+  </si>
+  <si>
+    <t>EP-2026-000037-SUR</t>
+  </si>
+  <si>
+    <t>FL-2026-000036-AGO</t>
+  </si>
+  <si>
+    <t>VO-2026-000035-VUT</t>
+  </si>
+  <si>
+    <t>VO-2026-000034-PHL</t>
+  </si>
+  <si>
+    <t>FL-2026-000033-ETH</t>
+  </si>
+  <si>
+    <t>CE-2026-000032-AFG</t>
+  </si>
+  <si>
+    <t>OT-2026-000031-CMR</t>
+  </si>
+  <si>
+    <t>FL-2026-000030-COD</t>
+  </si>
+  <si>
+    <t>EP-2026-000029-ZMB</t>
+  </si>
+  <si>
+    <t>FL-2026-000028-BRA</t>
+  </si>
+  <si>
+    <t>FL-2026-000027-ECU</t>
+  </si>
+  <si>
+    <t>CE-2026-000026-IRN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000025-BGD</t>
+  </si>
+  <si>
+    <t>CW-2026-000024-MNG</t>
+  </si>
+  <si>
+    <t>FL-2026-000023-ZWE</t>
+  </si>
+  <si>
+    <t>FR-2026-000022-CMR</t>
+  </si>
+  <si>
+    <t>FL-2026-000021-MWI</t>
+  </si>
+  <si>
+    <t>FL-2026-000020-ZMB</t>
+  </si>
+  <si>
+    <t>OT-2026-000019-LBN</t>
+  </si>
+  <si>
+    <t>FL-2026-000018-SYR</t>
+  </si>
+  <si>
+    <t>FL-2026-000017-COL</t>
+  </si>
+  <si>
+    <t>TC-2026-000015-MDG</t>
+  </si>
+  <si>
+    <t>EP-2026-000014-COM</t>
+  </si>
+  <si>
+    <t>CW-2026-000013-JPN</t>
+  </si>
+  <si>
+    <t>EP-2026-000012-GTM</t>
+  </si>
+  <si>
+    <t>FL-2026-000011-ZAF</t>
+  </si>
+  <si>
+    <t>FL-2026-000010-COD</t>
+  </si>
+  <si>
+    <t>TC-2026-000009-MDG</t>
+  </si>
+  <si>
+    <t>FL-2026-000008-DZA</t>
+  </si>
+  <si>
+    <t>LS-2026-000007-IDN</t>
+  </si>
+  <si>
     <t>FL-2026-000006-TUN</t>
   </si>
   <si>
@@ -61,6 +415,30 @@
     <t>FL-2026-000001-MYS</t>
   </si>
   <si>
+    <t>DR-2025-000238-MDG</t>
+  </si>
+  <si>
+    <t>FL-2025-000237-COD</t>
+  </si>
+  <si>
+    <t>DR-2025-000236-ARG</t>
+  </si>
+  <si>
+    <t>FL-2025-000235-BOL</t>
+  </si>
+  <si>
+    <t>DR-2025-000234-AGO</t>
+  </si>
+  <si>
+    <t>FL-2025-000233-IDN</t>
+  </si>
+  <si>
+    <t>EP-2025-000232-COK</t>
+  </si>
+  <si>
+    <t>ST-2025-000231-GAB</t>
+  </si>
+  <si>
     <t>EP-2025-000230-MDG</t>
   </si>
   <si>
@@ -1603,6 +1981,9 @@
     <t>EQ-2024-000001-JPN</t>
   </si>
   <si>
+    <t>FL-2023-000290-LBY</t>
+  </si>
+  <si>
     <t>TC-2023-000289-GUM</t>
   </si>
   <si>
@@ -3274,6 +3655,12 @@
     <t>EQ-2022-000001-CHN</t>
   </si>
   <si>
+    <t>TC-2021-000233-VNM</t>
+  </si>
+  <si>
+    <t>TC-2021-000232-MEX</t>
+  </si>
+  <si>
     <t>ST-2021-000231-KHM</t>
   </si>
   <si>
@@ -5065,6 +5452,12 @@
     <t>EQ-2020-000001-PRI</t>
   </si>
   <si>
+    <t>TC-2019-000202-IND</t>
+  </si>
+  <si>
+    <t>FL-2019-000201-MOZ</t>
+  </si>
+  <si>
     <t>AC-2019-000200-KHM</t>
   </si>
   <si>
@@ -5656,6 +6049,12 @@
     <t>TC-2019-000001-THA</t>
   </si>
   <si>
+    <t>FL-2018-000443-IND</t>
+  </si>
+  <si>
+    <t>FL-2018-000442-NGA</t>
+  </si>
+  <si>
     <t>CW-2018-000441-USA</t>
   </si>
   <si>
@@ -6194,6 +6593,15 @@
   </si>
   <si>
     <t>TC-2018-000001-MDG</t>
+  </si>
+  <si>
+    <t>FL-2017-000204-MDG</t>
+  </si>
+  <si>
+    <t>FL-2017-000203-BGD</t>
+  </si>
+  <si>
+    <t>FL-2017-000202-SLE</t>
   </si>
   <si>
     <t>ST-2017-000199-USA</t>
@@ -26292,7 +26700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8642"/>
+  <dimension ref="A1:G8778"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -95446,6 +95854,1094 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8643" spans="1:4">
+      <c r="A8643" t="s">
+        <v>8649</v>
+      </c>
+      <c r="D8643" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8644" spans="1:4">
+      <c r="A8644" t="s">
+        <v>8650</v>
+      </c>
+      <c r="D8644" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8645" spans="1:4">
+      <c r="A8645" t="s">
+        <v>8651</v>
+      </c>
+      <c r="D8645" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8646" spans="1:4">
+      <c r="A8646" t="s">
+        <v>8652</v>
+      </c>
+      <c r="D8646" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8647" spans="1:4">
+      <c r="A8647" t="s">
+        <v>8653</v>
+      </c>
+      <c r="D8647" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8648" spans="1:4">
+      <c r="A8648" t="s">
+        <v>8654</v>
+      </c>
+      <c r="D8648" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8649" spans="1:4">
+      <c r="A8649" t="s">
+        <v>8655</v>
+      </c>
+      <c r="D8649" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8650" spans="1:4">
+      <c r="A8650" t="s">
+        <v>8656</v>
+      </c>
+      <c r="D8650" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8651" spans="1:4">
+      <c r="A8651" t="s">
+        <v>8657</v>
+      </c>
+      <c r="D8651" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8652" spans="1:4">
+      <c r="A8652" t="s">
+        <v>8658</v>
+      </c>
+      <c r="D8652" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8653" spans="1:4">
+      <c r="A8653" t="s">
+        <v>8659</v>
+      </c>
+      <c r="D8653" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8654" spans="1:4">
+      <c r="A8654" t="s">
+        <v>8660</v>
+      </c>
+      <c r="D8654" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8655" spans="1:4">
+      <c r="A8655" t="s">
+        <v>8661</v>
+      </c>
+      <c r="D8655" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8656" spans="1:4">
+      <c r="A8656" t="s">
+        <v>8662</v>
+      </c>
+      <c r="D8656" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8657" spans="1:4">
+      <c r="A8657" t="s">
+        <v>8663</v>
+      </c>
+      <c r="D8657" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8658" spans="1:4">
+      <c r="A8658" t="s">
+        <v>8664</v>
+      </c>
+      <c r="D8658" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8659" spans="1:4">
+      <c r="A8659" t="s">
+        <v>8665</v>
+      </c>
+      <c r="D8659" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8660" spans="1:4">
+      <c r="A8660" t="s">
+        <v>8666</v>
+      </c>
+      <c r="D8660" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8661" spans="1:4">
+      <c r="A8661" t="s">
+        <v>8667</v>
+      </c>
+      <c r="D8661" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8662" spans="1:4">
+      <c r="A8662" t="s">
+        <v>8668</v>
+      </c>
+      <c r="D8662" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8663" spans="1:4">
+      <c r="A8663" t="s">
+        <v>8669</v>
+      </c>
+      <c r="D8663" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8664" spans="1:4">
+      <c r="A8664" t="s">
+        <v>8670</v>
+      </c>
+      <c r="D8664" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8665" spans="1:4">
+      <c r="A8665" t="s">
+        <v>8671</v>
+      </c>
+      <c r="D8665" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8666" spans="1:4">
+      <c r="A8666" t="s">
+        <v>8672</v>
+      </c>
+      <c r="D8666" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8667" spans="1:4">
+      <c r="A8667" t="s">
+        <v>8673</v>
+      </c>
+      <c r="D8667" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8668" spans="1:4">
+      <c r="A8668" t="s">
+        <v>8674</v>
+      </c>
+      <c r="D8668" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8669" spans="1:4">
+      <c r="A8669" t="s">
+        <v>8675</v>
+      </c>
+      <c r="D8669" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8670" spans="1:4">
+      <c r="A8670" t="s">
+        <v>8676</v>
+      </c>
+      <c r="D8670" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8671" spans="1:4">
+      <c r="A8671" t="s">
+        <v>8677</v>
+      </c>
+      <c r="D8671" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8672" spans="1:4">
+      <c r="A8672" t="s">
+        <v>8678</v>
+      </c>
+      <c r="D8672" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8673" spans="1:4">
+      <c r="A8673" t="s">
+        <v>8679</v>
+      </c>
+      <c r="D8673" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8674" spans="1:4">
+      <c r="A8674" t="s">
+        <v>8680</v>
+      </c>
+      <c r="D8674" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8675" spans="1:4">
+      <c r="A8675" t="s">
+        <v>8681</v>
+      </c>
+      <c r="D8675" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8676" spans="1:4">
+      <c r="A8676" t="s">
+        <v>8682</v>
+      </c>
+      <c r="D8676" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8677" spans="1:4">
+      <c r="A8677" t="s">
+        <v>8683</v>
+      </c>
+      <c r="D8677" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8678" spans="1:4">
+      <c r="A8678" t="s">
+        <v>8684</v>
+      </c>
+      <c r="D8678" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8679" spans="1:4">
+      <c r="A8679" t="s">
+        <v>8685</v>
+      </c>
+      <c r="D8679" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8680" spans="1:4">
+      <c r="A8680" t="s">
+        <v>8686</v>
+      </c>
+      <c r="D8680" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8681" spans="1:4">
+      <c r="A8681" t="s">
+        <v>8687</v>
+      </c>
+      <c r="D8681" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8682" spans="1:4">
+      <c r="A8682" t="s">
+        <v>8688</v>
+      </c>
+      <c r="D8682" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8683" spans="1:4">
+      <c r="A8683" t="s">
+        <v>8689</v>
+      </c>
+      <c r="D8683" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8684" spans="1:4">
+      <c r="A8684" t="s">
+        <v>8690</v>
+      </c>
+      <c r="D8684" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8685" spans="1:4">
+      <c r="A8685" t="s">
+        <v>8691</v>
+      </c>
+      <c r="D8685" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8686" spans="1:4">
+      <c r="A8686" t="s">
+        <v>8692</v>
+      </c>
+      <c r="D8686" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8687" spans="1:4">
+      <c r="A8687" t="s">
+        <v>8693</v>
+      </c>
+      <c r="D8687" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8688" spans="1:4">
+      <c r="A8688" t="s">
+        <v>8694</v>
+      </c>
+      <c r="D8688" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8689" spans="1:4">
+      <c r="A8689" t="s">
+        <v>8695</v>
+      </c>
+      <c r="D8689" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8690" spans="1:4">
+      <c r="A8690" t="s">
+        <v>8696</v>
+      </c>
+      <c r="D8690" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8691" spans="1:4">
+      <c r="A8691" t="s">
+        <v>8697</v>
+      </c>
+      <c r="D8691" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8692" spans="1:4">
+      <c r="A8692" t="s">
+        <v>8698</v>
+      </c>
+      <c r="D8692" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8693" spans="1:4">
+      <c r="A8693" t="s">
+        <v>8699</v>
+      </c>
+      <c r="D8693" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8694" spans="1:4">
+      <c r="A8694" t="s">
+        <v>8700</v>
+      </c>
+      <c r="D8694" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8695" spans="1:4">
+      <c r="A8695" t="s">
+        <v>8701</v>
+      </c>
+      <c r="D8695" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8696" spans="1:4">
+      <c r="A8696" t="s">
+        <v>8702</v>
+      </c>
+      <c r="D8696" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8697" spans="1:4">
+      <c r="A8697" t="s">
+        <v>8703</v>
+      </c>
+      <c r="D8697" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8698" spans="1:4">
+      <c r="A8698" t="s">
+        <v>8704</v>
+      </c>
+      <c r="D8698" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8699" spans="1:4">
+      <c r="A8699" t="s">
+        <v>8705</v>
+      </c>
+      <c r="D8699" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8700" spans="1:4">
+      <c r="A8700" t="s">
+        <v>8706</v>
+      </c>
+      <c r="D8700" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8701" spans="1:4">
+      <c r="A8701" t="s">
+        <v>8707</v>
+      </c>
+      <c r="D8701" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8702" spans="1:4">
+      <c r="A8702" t="s">
+        <v>8708</v>
+      </c>
+      <c r="D8702" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8703" spans="1:4">
+      <c r="A8703" t="s">
+        <v>8709</v>
+      </c>
+      <c r="D8703" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8704" spans="1:4">
+      <c r="A8704" t="s">
+        <v>8710</v>
+      </c>
+      <c r="D8704" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8705" spans="1:4">
+      <c r="A8705" t="s">
+        <v>8711</v>
+      </c>
+      <c r="D8705" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8706" spans="1:4">
+      <c r="A8706" t="s">
+        <v>8712</v>
+      </c>
+      <c r="D8706" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8707" spans="1:4">
+      <c r="A8707" t="s">
+        <v>8713</v>
+      </c>
+      <c r="D8707" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8708" spans="1:4">
+      <c r="A8708" t="s">
+        <v>8714</v>
+      </c>
+      <c r="D8708" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8709" spans="1:4">
+      <c r="A8709" t="s">
+        <v>8715</v>
+      </c>
+      <c r="D8709" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8710" spans="1:4">
+      <c r="A8710" t="s">
+        <v>8716</v>
+      </c>
+      <c r="D8710" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8711" spans="1:4">
+      <c r="A8711" t="s">
+        <v>8717</v>
+      </c>
+      <c r="D8711" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8712" spans="1:4">
+      <c r="A8712" t="s">
+        <v>8718</v>
+      </c>
+      <c r="D8712" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8713" spans="1:4">
+      <c r="A8713" t="s">
+        <v>8719</v>
+      </c>
+      <c r="D8713" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8714" spans="1:4">
+      <c r="A8714" t="s">
+        <v>8720</v>
+      </c>
+      <c r="D8714" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8715" spans="1:4">
+      <c r="A8715" t="s">
+        <v>8721</v>
+      </c>
+      <c r="D8715" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8716" spans="1:4">
+      <c r="A8716" t="s">
+        <v>8722</v>
+      </c>
+      <c r="D8716" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8717" spans="1:4">
+      <c r="A8717" t="s">
+        <v>8723</v>
+      </c>
+      <c r="D8717" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8718" spans="1:4">
+      <c r="A8718" t="s">
+        <v>8724</v>
+      </c>
+      <c r="D8718" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8719" spans="1:4">
+      <c r="A8719" t="s">
+        <v>8725</v>
+      </c>
+      <c r="D8719" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8720" spans="1:4">
+      <c r="A8720" t="s">
+        <v>8726</v>
+      </c>
+      <c r="D8720" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8721" spans="1:4">
+      <c r="A8721" t="s">
+        <v>8727</v>
+      </c>
+      <c r="D8721" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8722" spans="1:4">
+      <c r="A8722" t="s">
+        <v>8728</v>
+      </c>
+      <c r="D8722" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8723" spans="1:4">
+      <c r="A8723" t="s">
+        <v>8729</v>
+      </c>
+      <c r="D8723" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8724" spans="1:4">
+      <c r="A8724" t="s">
+        <v>8730</v>
+      </c>
+      <c r="D8724" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8725" spans="1:4">
+      <c r="A8725" t="s">
+        <v>8731</v>
+      </c>
+      <c r="D8725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8726" spans="1:4">
+      <c r="A8726" t="s">
+        <v>8732</v>
+      </c>
+      <c r="D8726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8727" spans="1:4">
+      <c r="A8727" t="s">
+        <v>8733</v>
+      </c>
+      <c r="D8727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8728" spans="1:4">
+      <c r="A8728" t="s">
+        <v>8734</v>
+      </c>
+      <c r="D8728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8729" spans="1:4">
+      <c r="A8729" t="s">
+        <v>8735</v>
+      </c>
+      <c r="D8729" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8730" spans="1:4">
+      <c r="A8730" t="s">
+        <v>8736</v>
+      </c>
+      <c r="D8730" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8731" spans="1:4">
+      <c r="A8731" t="s">
+        <v>8737</v>
+      </c>
+      <c r="D8731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8732" spans="1:4">
+      <c r="A8732" t="s">
+        <v>8738</v>
+      </c>
+      <c r="D8732" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8733" spans="1:4">
+      <c r="A8733" t="s">
+        <v>8739</v>
+      </c>
+      <c r="D8733" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8734" spans="1:4">
+      <c r="A8734" t="s">
+        <v>8740</v>
+      </c>
+      <c r="D8734" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8735" spans="1:4">
+      <c r="A8735" t="s">
+        <v>8741</v>
+      </c>
+      <c r="D8735" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8736" spans="1:4">
+      <c r="A8736" t="s">
+        <v>8742</v>
+      </c>
+      <c r="D8736" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8737" spans="1:4">
+      <c r="A8737" t="s">
+        <v>8743</v>
+      </c>
+      <c r="D8737" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8738" spans="1:4">
+      <c r="A8738" t="s">
+        <v>8744</v>
+      </c>
+      <c r="D8738" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8739" spans="1:4">
+      <c r="A8739" t="s">
+        <v>8745</v>
+      </c>
+      <c r="D8739" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8740" spans="1:4">
+      <c r="A8740" t="s">
+        <v>8746</v>
+      </c>
+      <c r="D8740" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8741" spans="1:4">
+      <c r="A8741" t="s">
+        <v>8747</v>
+      </c>
+      <c r="D8741" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8742" spans="1:4">
+      <c r="A8742" t="s">
+        <v>8748</v>
+      </c>
+      <c r="D8742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8743" spans="1:4">
+      <c r="A8743" t="s">
+        <v>8749</v>
+      </c>
+      <c r="D8743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8744" spans="1:4">
+      <c r="A8744" t="s">
+        <v>8750</v>
+      </c>
+      <c r="D8744" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8745" spans="1:4">
+      <c r="A8745" t="s">
+        <v>8751</v>
+      </c>
+      <c r="D8745" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8746" spans="1:4">
+      <c r="A8746" t="s">
+        <v>8752</v>
+      </c>
+      <c r="D8746" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8747" spans="1:4">
+      <c r="A8747" t="s">
+        <v>8753</v>
+      </c>
+      <c r="D8747" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8748" spans="1:4">
+      <c r="A8748" t="s">
+        <v>8754</v>
+      </c>
+      <c r="D8748" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8749" spans="1:4">
+      <c r="A8749" t="s">
+        <v>8755</v>
+      </c>
+      <c r="D8749" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8750" spans="1:4">
+      <c r="A8750" t="s">
+        <v>8756</v>
+      </c>
+      <c r="D8750" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8751" spans="1:4">
+      <c r="A8751" t="s">
+        <v>8757</v>
+      </c>
+      <c r="D8751" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8752" spans="1:4">
+      <c r="A8752" t="s">
+        <v>8758</v>
+      </c>
+      <c r="D8752" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8753" spans="1:4">
+      <c r="A8753" t="s">
+        <v>8759</v>
+      </c>
+      <c r="D8753" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8754" spans="1:4">
+      <c r="A8754" t="s">
+        <v>8760</v>
+      </c>
+      <c r="D8754" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8755" spans="1:4">
+      <c r="A8755" t="s">
+        <v>8761</v>
+      </c>
+      <c r="D8755" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8756" spans="1:4">
+      <c r="A8756" t="s">
+        <v>8762</v>
+      </c>
+      <c r="D8756" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8757" spans="1:4">
+      <c r="A8757" t="s">
+        <v>8763</v>
+      </c>
+      <c r="D8757" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8758" spans="1:4">
+      <c r="A8758" t="s">
+        <v>8764</v>
+      </c>
+      <c r="D8758" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8759" spans="1:4">
+      <c r="A8759" t="s">
+        <v>8765</v>
+      </c>
+      <c r="D8759" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8760" spans="1:4">
+      <c r="A8760" t="s">
+        <v>8766</v>
+      </c>
+      <c r="D8760" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8761" spans="1:4">
+      <c r="A8761" t="s">
+        <v>8767</v>
+      </c>
+      <c r="D8761" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8762" spans="1:4">
+      <c r="A8762" t="s">
+        <v>8768</v>
+      </c>
+      <c r="D8762" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8763" spans="1:4">
+      <c r="A8763" t="s">
+        <v>8769</v>
+      </c>
+      <c r="D8763" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8764" spans="1:4">
+      <c r="A8764" t="s">
+        <v>8770</v>
+      </c>
+      <c r="D8764" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8765" spans="1:4">
+      <c r="A8765" t="s">
+        <v>8771</v>
+      </c>
+      <c r="D8765" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8766" spans="1:4">
+      <c r="A8766" t="s">
+        <v>8772</v>
+      </c>
+      <c r="D8766" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8767" spans="1:4">
+      <c r="A8767" t="s">
+        <v>8773</v>
+      </c>
+      <c r="D8767" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8768" spans="1:4">
+      <c r="A8768" t="s">
+        <v>8774</v>
+      </c>
+      <c r="D8768" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8769" spans="1:4">
+      <c r="A8769" t="s">
+        <v>8775</v>
+      </c>
+      <c r="D8769" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8770" spans="1:4">
+      <c r="A8770" t="s">
+        <v>8776</v>
+      </c>
+      <c r="D8770" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8771" spans="1:4">
+      <c r="A8771" t="s">
+        <v>8777</v>
+      </c>
+      <c r="D8771" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8772" spans="1:4">
+      <c r="A8772" t="s">
+        <v>8778</v>
+      </c>
+      <c r="D8772" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8773" spans="1:4">
+      <c r="A8773" t="s">
+        <v>8779</v>
+      </c>
+      <c r="D8773" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8774" spans="1:4">
+      <c r="A8774" t="s">
+        <v>8780</v>
+      </c>
+      <c r="D8774" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8775" spans="1:4">
+      <c r="A8775" t="s">
+        <v>8781</v>
+      </c>
+      <c r="D8775" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8776" spans="1:4">
+      <c r="A8776" t="s">
+        <v>8782</v>
+      </c>
+      <c r="D8776" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8777" spans="1:4">
+      <c r="A8777" t="s">
+        <v>8783</v>
+      </c>
+      <c r="D8777" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8778" spans="1:4">
+      <c r="A8778" t="s">
+        <v>8784</v>
+      </c>
+      <c r="D8778" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17561" uniqueCount="8785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17571" uniqueCount="8790">
   <si>
     <t>code</t>
   </si>
@@ -43,6 +43,15 @@
     <t>en</t>
   </si>
   <si>
+    <t>DR-2026-000117-ETH</t>
+  </si>
+  <si>
+    <t>WF-2026-000116-KAZ</t>
+  </si>
+  <si>
+    <t>VO-2026-000115-PHL</t>
+  </si>
+  <si>
     <t>FL-2026-000114-KGZ</t>
   </si>
   <si>
@@ -103,6 +112,9 @@
     <t>TC-2026-000098-CHN</t>
   </si>
   <si>
+    <t>TC-2026-000098-LAO</t>
+  </si>
+  <si>
     <t>TC-2026-000098-VNM</t>
   </si>
   <si>
@@ -413,6 +425,9 @@
   </si>
   <si>
     <t>FL-2026-000001-MYS</t>
+  </si>
+  <si>
+    <t>DR-2025-000239-ALB</t>
   </si>
   <si>
     <t>DR-2025-000238-MDG</t>
@@ -26700,7 +26715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8778"/>
+  <dimension ref="A1:G8783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -96942,6 +96957,46 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8779" spans="1:4">
+      <c r="A8779" t="s">
+        <v>8785</v>
+      </c>
+      <c r="D8779" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8780" spans="1:4">
+      <c r="A8780" t="s">
+        <v>8786</v>
+      </c>
+      <c r="D8780" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8781" spans="1:4">
+      <c r="A8781" t="s">
+        <v>8787</v>
+      </c>
+      <c r="D8781" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8782" spans="1:4">
+      <c r="A8782" t="s">
+        <v>8788</v>
+      </c>
+      <c r="D8782" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8783" spans="1:4">
+      <c r="A8783" t="s">
+        <v>8789</v>
+      </c>
+      <c r="D8783" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17571" uniqueCount="8790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17609" uniqueCount="8809">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,63 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>WF-2026-000138-DZA</t>
+  </si>
+  <si>
+    <t>FL-2026-000137-VNM</t>
+  </si>
+  <si>
+    <t>FL-2026-000136-CHN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000135-JPN</t>
+  </si>
+  <si>
+    <t>EP-2026-000134-TCD</t>
+  </si>
+  <si>
+    <t>TC-2026-000133-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000133-PHL</t>
+  </si>
+  <si>
+    <t>WF-2026-000132-TUN</t>
+  </si>
+  <si>
+    <t>WF-2026-000131-ESP</t>
+  </si>
+  <si>
+    <t>WF-2026-000130-ESP</t>
+  </si>
+  <si>
+    <t>WF-2026-000129-FRA</t>
+  </si>
+  <si>
+    <t>WF-2026-000128-ESP</t>
+  </si>
+  <si>
+    <t>FF-2026-000127-CHN</t>
+  </si>
+  <si>
+    <t>WF-2026-000126-TUR</t>
+  </si>
+  <si>
+    <t>FF-2026-000122-USA</t>
+  </si>
+  <si>
+    <t>FL-2026-000121-IND</t>
+  </si>
+  <si>
+    <t>FF-2026-000120-AFG</t>
+  </si>
+  <si>
+    <t>WF-2026-000119-CAN</t>
+  </si>
+  <si>
+    <t>LS-2026-000118-CHN</t>
   </si>
   <si>
     <t>DR-2026-000117-ETH</t>
@@ -26715,7 +26772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8783"/>
+  <dimension ref="A1:G8802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -96997,6 +97054,158 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8784" spans="1:4">
+      <c r="A8784" t="s">
+        <v>8790</v>
+      </c>
+      <c r="D8784" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8785" spans="1:4">
+      <c r="A8785" t="s">
+        <v>8791</v>
+      </c>
+      <c r="D8785" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8786" spans="1:4">
+      <c r="A8786" t="s">
+        <v>8792</v>
+      </c>
+      <c r="D8786" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8787" spans="1:4">
+      <c r="A8787" t="s">
+        <v>8793</v>
+      </c>
+      <c r="D8787" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8788" spans="1:4">
+      <c r="A8788" t="s">
+        <v>8794</v>
+      </c>
+      <c r="D8788" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8789" spans="1:4">
+      <c r="A8789" t="s">
+        <v>8795</v>
+      </c>
+      <c r="D8789" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8790" spans="1:4">
+      <c r="A8790" t="s">
+        <v>8796</v>
+      </c>
+      <c r="D8790" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8791" spans="1:4">
+      <c r="A8791" t="s">
+        <v>8797</v>
+      </c>
+      <c r="D8791" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8792" spans="1:4">
+      <c r="A8792" t="s">
+        <v>8798</v>
+      </c>
+      <c r="D8792" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8793" spans="1:4">
+      <c r="A8793" t="s">
+        <v>8799</v>
+      </c>
+      <c r="D8793" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8794" spans="1:4">
+      <c r="A8794" t="s">
+        <v>8800</v>
+      </c>
+      <c r="D8794" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8795" spans="1:4">
+      <c r="A8795" t="s">
+        <v>8801</v>
+      </c>
+      <c r="D8795" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8796" spans="1:4">
+      <c r="A8796" t="s">
+        <v>8802</v>
+      </c>
+      <c r="D8796" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8797" spans="1:4">
+      <c r="A8797" t="s">
+        <v>8803</v>
+      </c>
+      <c r="D8797" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8798" spans="1:4">
+      <c r="A8798" t="s">
+        <v>8804</v>
+      </c>
+      <c r="D8798" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8799" spans="1:4">
+      <c r="A8799" t="s">
+        <v>8805</v>
+      </c>
+      <c r="D8799" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8800" spans="1:4">
+      <c r="A8800" t="s">
+        <v>8806</v>
+      </c>
+      <c r="D8800" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8801" spans="1:4">
+      <c r="A8801" t="s">
+        <v>8807</v>
+      </c>
+      <c r="D8801" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8802" spans="1:4">
+      <c r="A8802" t="s">
+        <v>8808</v>
+      </c>
+      <c r="D8802" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17609" uniqueCount="8809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17621" uniqueCount="8815">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,24 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>TC-2026-000144-JPN</t>
+  </si>
+  <si>
+    <t>DR-2026-000143-COD</t>
+  </si>
+  <si>
+    <t>WF-2026-000142-GRC</t>
+  </si>
+  <si>
+    <t>FL-2026-000141-MMR</t>
+  </si>
+  <si>
+    <t>WF-2026-000140-GRC</t>
+  </si>
+  <si>
+    <t>FF-2026-000139-IND</t>
   </si>
   <si>
     <t>WF-2026-000138-DZA</t>
@@ -26772,7 +26790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8802"/>
+  <dimension ref="A1:G8808"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -97206,6 +97224,54 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8803" spans="1:4">
+      <c r="A8803" t="s">
+        <v>8809</v>
+      </c>
+      <c r="D8803" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8804" spans="1:4">
+      <c r="A8804" t="s">
+        <v>8810</v>
+      </c>
+      <c r="D8804" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8805" spans="1:4">
+      <c r="A8805" t="s">
+        <v>8811</v>
+      </c>
+      <c r="D8805" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8806" spans="1:4">
+      <c r="A8806" t="s">
+        <v>8812</v>
+      </c>
+      <c r="D8806" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8807" spans="1:4">
+      <c r="A8807" t="s">
+        <v>8813</v>
+      </c>
+      <c r="D8807" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8808" spans="1:4">
+      <c r="A8808" t="s">
+        <v>8814</v>
+      </c>
+      <c r="D8808" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/2/clv1/codelist/GLIDENumber.xlsx
+++ b/api/2/clv1/codelist/GLIDENumber.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17621" uniqueCount="8815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17677" uniqueCount="8843">
   <si>
     <t>code</t>
   </si>
@@ -41,6 +41,90 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>FL-2026-000170-JPN</t>
+  </si>
+  <si>
+    <t>FL-2026-000169-PHL</t>
+  </si>
+  <si>
+    <t>EQ-2026-000168-CHN</t>
+  </si>
+  <si>
+    <t>FL-2026-000167-NPL</t>
+  </si>
+  <si>
+    <t>FL-2026-000166-CHN</t>
+  </si>
+  <si>
+    <t>FL-2026-000165-IND</t>
+  </si>
+  <si>
+    <t>FL-2026-000164-KHM</t>
+  </si>
+  <si>
+    <t>FL-2026-000163-TWN</t>
+  </si>
+  <si>
+    <t>FF-2026-000162-NPL</t>
+  </si>
+  <si>
+    <t>MS-2026-000162-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000161-CHN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000160-AFG</t>
+  </si>
+  <si>
+    <t>DR-2026-000159-HND</t>
+  </si>
+  <si>
+    <t>FL-2026-000158-THA</t>
+  </si>
+  <si>
+    <t>TC-2026-000157-CHN</t>
+  </si>
+  <si>
+    <t>TC-2026-000157-VNM</t>
+  </si>
+  <si>
+    <t>WF-2026-000156-SRB</t>
+  </si>
+  <si>
+    <t>WF-2026-000155-BEL</t>
+  </si>
+  <si>
+    <t>WF-2026-000154-ESP</t>
+  </si>
+  <si>
+    <t>DR-2026-000153-BLZ</t>
+  </si>
+  <si>
+    <t>FF-2026-000152-SLE</t>
+  </si>
+  <si>
+    <t>EQ-2026-000150-IDN</t>
+  </si>
+  <si>
+    <t>FL-2026-000149-LKA</t>
+  </si>
+  <si>
+    <t>FL-2026-000148-CHN</t>
+  </si>
+  <si>
+    <t>WF-2026-000147-CAN</t>
+  </si>
+  <si>
+    <t>EQ-2026-000146-COL</t>
+  </si>
+  <si>
+    <t>WF-2026-000145-TUN</t>
+  </si>
+  <si>
+    <t>TC-2026-000144-CHN</t>
   </si>
   <si>
     <t>TC-2026-000144-JPN</t>
@@ -26790,7 +26874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8808"/>
+  <dimension ref="A1:G8836"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -97272,6 +97356,230 @@
         <v>8</v>
       </c>
     </row>
+    <row r="8809" spans="1:4">
+      <c r="A8809" t="s">
+        <v>8815</v>
+      </c>
+      <c r="D8809" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8810" spans="1:4">
+      <c r="A8810" t="s">
+        <v>8816</v>
+      </c>
+      <c r="D8810" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8811" spans="1:4">
+      <c r="A8811" t="s">
+        <v>8817</v>
+      </c>
+      <c r="D8811" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8812" spans="1:4">
+      <c r="A8812" t="s">
+        <v>8818</v>
+      </c>
+      <c r="D8812" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8813" spans="1:4">
+      <c r="A8813" t="s">
+        <v>8819</v>
+      </c>
+      <c r="D8813" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8814" spans="1:4">
+      <c r="A8814" t="s">
+        <v>8820</v>
+      </c>
+      <c r="D8814" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8815" spans="1:4">
+      <c r="A8815" t="s">
+        <v>8821</v>
+      </c>
+      <c r="D8815" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8816" spans="1:4">
+      <c r="A8816" t="s">
+        <v>8822</v>
+      </c>
+      <c r="D8816" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8817" spans="1:4">
+      <c r="A8817" t="s">
+        <v>8823</v>
+      </c>
+      <c r="D8817" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8818" spans="1:4">
+      <c r="A8818" t="s">
+        <v>8824</v>
+      </c>
+      <c r="D8818" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8819" spans="1:4">
+      <c r="A8819" t="s">
+        <v>8825</v>
+      </c>
+      <c r="D8819" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8820" spans="1:4">
+      <c r="A8820" t="s">
+        <v>8826</v>
+      </c>
+      <c r="D8820" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8821" spans="1:4">
+      <c r="A8821" t="s">
+        <v>8827</v>
+      </c>
+      <c r="D8821" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8822" spans="1:4">
+      <c r="A8822" t="s">
+        <v>8828</v>
+      </c>
+      <c r="D8822" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8823" spans="1:4">
+      <c r="A8823" t="s">
+        <v>8829</v>
+      </c>
+      <c r="D8823" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8824" spans="1:4">
+      <c r="A8824" t="s">
+        <v>8830</v>
+      </c>
+      <c r="D8824" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8825" spans="1:4">
+      <c r="A8825" t="s">
+        <v>8831</v>
+      </c>
+      <c r="D8825" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8826" spans="1:4">
+      <c r="A8826" t="s">
+        <v>8832</v>
+      </c>
+      <c r="D8826" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8827" spans="1:4">
+      <c r="A8827" t="s">
+        <v>8833</v>
+      </c>
+      <c r="D8827" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8828" spans="1:4">
+      <c r="A8828" t="s">
+        <v>8834</v>
+      </c>
+      <c r="D8828" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8829" spans="1:4">
+      <c r="A8829" t="s">
+        <v>8835</v>
+      </c>
+      <c r="D8829" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8830" spans="1:4">
+      <c r="A8830" t="s">
+        <v>8836</v>
+      </c>
+      <c r="D8830" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8831" spans="1:4">
+      <c r="A8831" t="s">
+        <v>8837</v>
+      </c>
+      <c r="D8831" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8832" spans="1:4">
+      <c r="A8832" t="s">
+        <v>8838</v>
+      </c>
+      <c r="D8832" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8833" spans="1:4">
+      <c r="A8833" t="s">
+        <v>8839</v>
+      </c>
+      <c r="D8833" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8834" spans="1:4">
+      <c r="A8834" t="s">
+        <v>8840</v>
+      </c>
+      <c r="D8834" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8835" spans="1:4">
+      <c r="A8835" t="s">
+        <v>8841</v>
+      </c>
+      <c r="D8835" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8836" spans="1:4">
+      <c r="A8836" t="s">
+        <v>8842</v>
+      </c>
+      <c r="D8836" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
